--- a/nriss-patch-2/ig/StructureDefinition-fr-medication-statement-document.xlsx
+++ b/nriss-patch-2/ig/StructureDefinition-fr-medication-statement-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T15:58:47+00:00</t>
+    <t>2026-08-04T07:44:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nriss-patch-2/ig/StructureDefinition-fr-medication-statement-document.xlsx
+++ b/nriss-patch-2/ig/StructureDefinition-fr-medication-statement-document.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$60</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1986" uniqueCount="443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2200" uniqueCount="469">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T07:44:41+00:00</t>
+    <t>2026-08-07T09:15:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -862,6 +862,121 @@
     <t>.inboundRelationship[typeCode=SUBJ]/source[classCode=OBS,moodCode=EVN,code="annotation"].value</t>
   </si>
   <si>
+    <t>MedicationStatement.note.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>MedicationStatement.note.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>MedicationStatement.note.extension:adherence</t>
+  </si>
+  <si>
+    <t>adherence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationStatement.adherence|0.1.0}
+</t>
+  </si>
+  <si>
+    <t>Statut de prise du médicament</t>
+  </si>
+  <si>
+    <t>R5: `MedicationStatement.adherence` (new:BackboneElement)</t>
+  </si>
+  <si>
+    <t>Element `MedicationStatement.adherence` has a context of MedicationStatement based on following the parent source element upwards and mapping to `MedicationStatement`.
+Element `MedicationStatement.adherence` has no mapping targets in FHIR R4. Typically, this is because the element has been added (is a new element).
+This element can be used to indicate whether a patient is following a course of treatment as instructed/prescribed or whether they are taking medications of their own volition.  It can also be used to indicate that a patient is not taking a medication, either because they were told not to or because they decided on their own.</t>
+  </si>
+  <si>
+    <t>MedicationStatement.note.author[x]</t>
+  </si>
+  <si>
+    <t>Reference(Practitioner|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1|Organization|4.0.1)
+string</t>
+  </si>
+  <si>
+    <t>Individual responsible for the annotation</t>
+  </si>
+  <si>
+    <t>The individual responsible for making the annotation.</t>
+  </si>
+  <si>
+    <t>Organization is used when there's no need for specific attribution as to who made the comment.</t>
+  </si>
+  <si>
+    <t>Annotation.author[x]</t>
+  </si>
+  <si>
+    <t>Act.participant[typeCode=AUT].role</t>
+  </si>
+  <si>
+    <t>MedicationStatement.note.time</t>
+  </si>
+  <si>
+    <t>When the annotation was made</t>
+  </si>
+  <si>
+    <t>Indicates when this particular annotation was made.</t>
+  </si>
+  <si>
+    <t>Annotation.time</t>
+  </si>
+  <si>
+    <t>Act.effectiveTime</t>
+  </si>
+  <si>
+    <t>MedicationStatement.note.text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">markdown
+</t>
+  </si>
+  <si>
+    <t>The annotation  - text content (as markdown)</t>
+  </si>
+  <si>
+    <t>The text of the annotation in markdown format.</t>
+  </si>
+  <si>
+    <t>Annotation.text</t>
+  </si>
+  <si>
+    <t>Act.text</t>
+  </si>
+  <si>
     <t>MedicationStatement.dosage</t>
   </si>
   <si>
@@ -884,39 +999,7 @@
     <t>MedicationStatement.dosage.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>MedicationStatement.dosage.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>MedicationStatement.dosage.modifierExtension</t>
@@ -1721,7 +1804,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN54"/>
+  <dimension ref="A1:AN60"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="52.38671875" customWidth="true" bestFit="true"/>
@@ -4725,7 +4808,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
         <v>267</v>
       </c>
@@ -4741,10 +4824,10 @@
         <v>78</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>77</v>
@@ -4761,9 +4844,7 @@
       <c r="M27" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="N27" t="s" s="2">
-        <v>271</v>
-      </c>
+      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>77</v>
@@ -4812,19 +4893,19 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>77</v>
@@ -4848,14 +4929,14 @@
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>77</v>
+        <v>133</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>77</v>
@@ -4867,15 +4948,17 @@
         <v>77</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="L28" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="N28" s="2"/>
+      <c r="N28" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>77</v>
@@ -4912,37 +4995,37 @@
         <v>77</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>77</v>
+        <v>275</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>77</v>
+        <v>276</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>77</v>
+        <v>277</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>77</v>
+        <v>139</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>77</v>
@@ -4951,26 +5034,28 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
         <v>279</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="C29" s="2"/>
+        <v>273</v>
+      </c>
+      <c r="C29" t="s" s="2">
+        <v>280</v>
+      </c>
       <c r="D29" t="s" s="2">
-        <v>133</v>
+        <v>77</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>77</v>
@@ -4979,16 +5064,16 @@
         <v>77</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>134</v>
+        <v>281</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>135</v>
+        <v>282</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>137</v>
+        <v>284</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5026,19 +5111,19 @@
         <v>77</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>281</v>
+        <v>77</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>282</v>
+        <v>77</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>283</v>
+        <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5056,7 +5141,7 @@
         <v>77</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>278</v>
+        <v>77</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>77</v>
@@ -5074,26 +5159,26 @@
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>286</v>
+        <v>77</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J30" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>134</v>
+        <v>286</v>
       </c>
       <c r="L30" t="s" s="2">
         <v>287</v>
@@ -5102,11 +5187,9 @@
         <v>288</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>77</v>
       </c>
@@ -5154,39 +5237,39 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL30" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="AM30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN30" t="s" s="2">
         <v>131</v>
       </c>
-      <c r="AM30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>77</v>
-      </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5200,7 +5283,7 @@
         <v>88</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>77</v>
@@ -5209,18 +5292,16 @@
         <v>89</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>291</v>
+        <v>228</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N31" s="2"/>
-      <c r="O31" t="s" s="2">
-        <v>294</v>
-      </c>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>77</v>
       </c>
@@ -5292,15 +5373,15 @@
         <v>77</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>297</v>
+        <v>131</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5308,7 +5389,7 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>88</v>
@@ -5323,7 +5404,7 @@
         <v>89</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>274</v>
+        <v>298</v>
       </c>
       <c r="L32" t="s" s="2">
         <v>299</v>
@@ -5332,9 +5413,7 @@
         <v>300</v>
       </c>
       <c r="N32" s="2"/>
-      <c r="O32" t="s" s="2">
-        <v>301</v>
-      </c>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>77</v>
       </c>
@@ -5382,10 +5461,10 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH32" t="s" s="2">
         <v>88</v>
@@ -5400,21 +5479,21 @@
         <v>77</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>303</v>
+        <v>131</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5434,10 +5513,10 @@
         <v>77</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>179</v>
+        <v>304</v>
       </c>
       <c r="L33" t="s" s="2">
         <v>305</v>
@@ -5448,9 +5527,7 @@
       <c r="N33" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="O33" t="s" s="2">
-        <v>308</v>
-      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>77</v>
       </c>
@@ -5474,13 +5551,13 @@
         <v>77</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>183</v>
+        <v>77</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>309</v>
+        <v>77</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>310</v>
+        <v>77</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>77</v>
@@ -5498,7 +5575,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5516,21 +5593,21 @@
         <v>77</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>312</v>
+        <v>77</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5553,13 +5630,13 @@
         <v>77</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5610,7 +5687,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5628,7 +5705,7 @@
         <v>77</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>77</v>
@@ -5639,10 +5716,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5671,7 +5748,7 @@
         <v>135</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="N35" t="s" s="2">
         <v>137</v>
@@ -5712,19 +5789,19 @@
         <v>77</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5742,7 +5819,7 @@
         <v>77</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>77</v>
@@ -5753,14 +5830,14 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>77</v>
+        <v>312</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -5773,25 +5850,25 @@
         <v>77</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="J36" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>316</v>
+        <v>134</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>319</v>
+        <v>137</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>320</v>
+        <v>143</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>77</v>
@@ -5840,7 +5917,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5852,27 +5929,27 @@
         <v>77</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>322</v>
+        <v>131</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>323</v>
+        <v>77</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5895,19 +5972,17 @@
         <v>89</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>274</v>
+        <v>317</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>327</v>
-      </c>
+        <v>319</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>77</v>
@@ -5956,7 +6031,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5974,21 +6049,21 @@
         <v>77</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>331</v>
+        <v>323</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6011,16 +6086,18 @@
         <v>89</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="N38" s="2"/>
-      <c r="O38" s="2"/>
+      <c r="O38" t="s" s="2">
+        <v>327</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>77</v>
       </c>
@@ -6068,7 +6145,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6086,21 +6163,21 @@
         <v>77</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>296</v>
+        <v>322</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>312</v>
+        <v>329</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6111,7 +6188,7 @@
         <v>78</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>89</v>
@@ -6123,19 +6200,19 @@
         <v>89</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>337</v>
+        <v>179</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>77</v>
@@ -6160,13 +6237,13 @@
         <v>77</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>77</v>
+        <v>183</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>77</v>
+        <v>335</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>77</v>
+        <v>336</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>77</v>
@@ -6184,13 +6261,13 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>77</v>
@@ -6202,21 +6279,21 @@
         <v>77</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>225</v>
+        <v>322</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>77</v>
+        <v>338</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6230,26 +6307,24 @@
         <v>88</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>344</v>
+        <v>268</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>345</v>
+        <v>269</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>347</v>
-      </c>
+        <v>270</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>77</v>
@@ -6274,13 +6349,13 @@
         <v>77</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>183</v>
+        <v>77</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>348</v>
+        <v>77</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>349</v>
+        <v>77</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>77</v>
@@ -6298,7 +6373,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>350</v>
+        <v>271</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6310,63 +6385,61 @@
         <v>77</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>351</v>
+        <v>272</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>352</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>353</v>
+        <v>340</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>353</v>
+        <v>340</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>77</v>
+        <v>133</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>179</v>
+        <v>134</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>354</v>
+        <v>135</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>355</v>
+        <v>274</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>357</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>77</v>
       </c>
@@ -6390,61 +6463,63 @@
         <v>77</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="Y41" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="Y41" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="Z41" t="s" s="2">
-        <v>358</v>
+        <v>77</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>77</v>
+        <v>275</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>77</v>
+        <v>276</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>77</v>
+        <v>277</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>359</v>
+        <v>278</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>360</v>
+        <v>272</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>361</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>362</v>
+        <v>341</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>362</v>
+        <v>341</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6455,10 +6530,10 @@
         <v>78</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>77</v>
@@ -6467,17 +6542,19 @@
         <v>89</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>179</v>
+        <v>342</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>363</v>
+        <v>343</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="N42" s="2"/>
+        <v>344</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>345</v>
+      </c>
       <c r="O42" t="s" s="2">
-        <v>365</v>
+        <v>346</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>77</v>
@@ -6502,13 +6579,13 @@
         <v>77</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>172</v>
+        <v>77</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>366</v>
+        <v>77</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>367</v>
+        <v>77</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>77</v>
@@ -6526,13 +6603,13 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>368</v>
+        <v>347</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>77</v>
@@ -6544,21 +6621,21 @@
         <v>77</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>369</v>
+        <v>348</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>370</v>
+        <v>349</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
-        <v>371</v>
+        <v>350</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>371</v>
+        <v>350</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6572,7 +6649,7 @@
         <v>88</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>77</v>
@@ -6581,19 +6658,19 @@
         <v>89</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>179</v>
+        <v>268</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>372</v>
+        <v>351</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>373</v>
+        <v>352</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>374</v>
+        <v>353</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>375</v>
+        <v>354</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>77</v>
@@ -6618,13 +6695,13 @@
         <v>77</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>183</v>
+        <v>77</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>376</v>
+        <v>77</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>377</v>
+        <v>77</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>77</v>
@@ -6642,7 +6719,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>378</v>
+        <v>355</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6660,21 +6737,21 @@
         <v>77</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>379</v>
+        <v>356</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>380</v>
+        <v>357</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>381</v>
+        <v>358</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>381</v>
+        <v>358</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6685,10 +6762,10 @@
         <v>78</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>77</v>
@@ -6697,13 +6774,13 @@
         <v>89</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>382</v>
+        <v>268</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>384</v>
+        <v>360</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6754,13 +6831,13 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>385</v>
+        <v>361</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>77</v>
@@ -6772,21 +6849,21 @@
         <v>77</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>77</v>
+        <v>322</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>386</v>
+        <v>338</v>
       </c>
     </row>
-    <row r="45" hidden="true">
+    <row r="45">
       <c r="A45" t="s" s="2">
-        <v>387</v>
+        <v>362</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>387</v>
+        <v>362</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6800,25 +6877,29 @@
         <v>88</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>274</v>
+        <v>363</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>275</v>
+        <v>364</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
+        <v>365</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>367</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>77</v>
       </c>
@@ -6866,7 +6947,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>277</v>
+        <v>368</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6878,13 +6959,13 @@
         <v>77</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>278</v>
+        <v>225</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>77</v>
@@ -6893,44 +6974,44 @@
         <v>77</v>
       </c>
     </row>
-    <row r="46" hidden="true">
+    <row r="46">
       <c r="A46" t="s" s="2">
-        <v>388</v>
+        <v>369</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>388</v>
+        <v>369</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>133</v>
+        <v>77</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>134</v>
+        <v>370</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>135</v>
+        <v>371</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>280</v>
+        <v>372</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>137</v>
+        <v>373</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6956,63 +7037,63 @@
         <v>77</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>77</v>
+        <v>183</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>77</v>
+        <v>374</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>77</v>
+        <v>375</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>281</v>
+        <v>77</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>282</v>
+        <v>77</v>
       </c>
       <c r="AD46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>283</v>
+        <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>284</v>
+        <v>376</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>278</v>
+        <v>377</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>77</v>
+        <v>378</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7026,7 +7107,7 @@
         <v>88</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>77</v>
@@ -7038,14 +7119,16 @@
         <v>179</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>381</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>382</v>
+      </c>
       <c r="O47" t="s" s="2">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>77</v>
@@ -7070,13 +7153,11 @@
         <v>77</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="Y47" t="s" s="2">
-        <v>393</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="Y47" s="2"/>
       <c r="Z47" t="s" s="2">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>77</v>
@@ -7094,7 +7175,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>395</v>
+        <v>385</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7112,21 +7193,21 @@
         <v>77</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>77</v>
+        <v>386</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>396</v>
+        <v>387</v>
       </c>
     </row>
-    <row r="48" hidden="true">
+    <row r="48">
       <c r="A48" t="s" s="2">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7140,7 +7221,7 @@
         <v>88</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>77</v>
@@ -7149,19 +7230,17 @@
         <v>89</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>398</v>
+        <v>179</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>401</v>
-      </c>
+        <v>390</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>402</v>
+        <v>391</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>77</v>
@@ -7186,29 +7265,31 @@
         <v>77</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>77</v>
+        <v>172</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>77</v>
+        <v>392</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>77</v>
+        <v>393</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="AC48" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="AD48" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>283</v>
+        <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>404</v>
+        <v>394</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7226,25 +7307,23 @@
         <v>77</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>379</v>
+        <v>395</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>405</v>
+        <v>396</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>406</v>
+        <v>397</v>
       </c>
       <c r="B49" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="C49" t="s" s="2">
-        <v>407</v>
-      </c>
+      <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
         <v>77</v>
       </c>
@@ -7256,7 +7335,7 @@
         <v>88</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>77</v>
@@ -7265,19 +7344,19 @@
         <v>89</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>408</v>
+        <v>179</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>409</v>
+        <v>398</v>
       </c>
       <c r="M49" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="N49" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="N49" t="s" s="2">
+      <c r="O49" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>77</v>
@@ -7302,13 +7381,13 @@
         <v>77</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>77</v>
+        <v>183</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>77</v>
+        <v>402</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>77</v>
+        <v>403</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>77</v>
@@ -7344,21 +7423,21 @@
         <v>77</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>379</v>
+        <v>405</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
-    <row r="50" hidden="true">
+    <row r="50">
       <c r="A50" t="s" s="2">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7369,10 +7448,10 @@
         <v>78</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>77</v>
@@ -7381,20 +7460,16 @@
         <v>89</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>415</v>
-      </c>
+        <v>410</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>77</v>
       </c>
@@ -7430,23 +7505,25 @@
         <v>77</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="AC50" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="AD50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>283</v>
+        <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>77</v>
@@ -7458,25 +7535,23 @@
         <v>77</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>417</v>
+        <v>77</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>418</v>
+        <v>412</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="C51" t="s" s="2">
-        <v>420</v>
-      </c>
+        <v>413</v>
+      </c>
+      <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
         <v>77</v>
       </c>
@@ -7488,29 +7563,25 @@
         <v>88</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>408</v>
+        <v>268</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>421</v>
+        <v>269</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>415</v>
-      </c>
+        <v>270</v>
+      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>77</v>
       </c>
@@ -7558,7 +7629,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>416</v>
+        <v>271</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7570,63 +7641,61 @@
         <v>77</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>417</v>
+        <v>272</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>418</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>77</v>
+        <v>133</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>423</v>
+        <v>134</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>424</v>
+        <v>135</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>425</v>
+        <v>274</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>427</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>77</v>
       </c>
@@ -7662,51 +7731,51 @@
         <v>77</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>77</v>
+        <v>275</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>77</v>
+        <v>276</v>
       </c>
       <c r="AD52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>77</v>
+        <v>277</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>428</v>
+        <v>278</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>429</v>
+        <v>272</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>430</v>
+        <v>77</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>431</v>
+        <v>415</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>431</v>
+        <v>415</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7729,19 +7798,17 @@
         <v>89</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>408</v>
+        <v>179</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>432</v>
+        <v>416</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>434</v>
-      </c>
+        <v>417</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>435</v>
+        <v>418</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>77</v>
@@ -7766,13 +7833,13 @@
         <v>77</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>77</v>
+        <v>183</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>77</v>
+        <v>419</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>77</v>
+        <v>420</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>77</v>
@@ -7790,7 +7857,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>436</v>
+        <v>421</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7808,21 +7875,21 @@
         <v>77</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>437</v>
+        <v>77</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>77</v>
+        <v>422</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>438</v>
+        <v>423</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>438</v>
+        <v>423</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7845,17 +7912,19 @@
         <v>89</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>408</v>
+        <v>424</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>439</v>
+        <v>425</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>426</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>427</v>
+      </c>
       <c r="O54" t="s" s="2">
-        <v>441</v>
+        <v>428</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>77</v>
@@ -7892,19 +7961,17 @@
         <v>77</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC54" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>429</v>
+      </c>
+      <c r="AC54" s="2"/>
       <c r="AD54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>77</v>
+        <v>277</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>442</v>
+        <v>430</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -7922,17 +7989,713 @@
         <v>77</v>
       </c>
       <c r="AL54" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN54" t="s" s="2">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="C55" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="D55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E55" s="2"/>
+      <c r="F55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J55" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K55" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="P55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q55" s="2"/>
+      <c r="R55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF55" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="56" hidden="true">
+      <c r="A56" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E56" s="2"/>
+      <c r="F56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J56" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K56" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="AM54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN54" t="s" s="2">
+      <c r="L56" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="P56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q56" s="2"/>
+      <c r="R56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AC56" s="2"/>
+      <c r="AD56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="AF56" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN56" t="s" s="2">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="C57" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="D57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E57" s="2"/>
+      <c r="F57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K57" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="P57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q57" s="2"/>
+      <c r="R57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF57" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="P58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="59" hidden="true">
+      <c r="A59" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="P59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="60" hidden="true">
+      <c r="A60" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="P60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN60" t="s" s="2">
         <v>77</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN54">
+  <autoFilter ref="A1:AN60">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -7942,7 +8705,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI53">
+  <conditionalFormatting sqref="A2:AI59">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
